--- a/data/trans_dic/KIDMED_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>1,69; 12,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 13,32</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,25</t>
+          <t>1,11; 6,57</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>1,19; 6,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,97</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,27</t>
+          <t>0,65; 3,29</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,2</t>
+          <t>0,47; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,91</t>
+          <t>1,4; 6,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,63</t>
+          <t>1,13; 3,95</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>4,33%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,64</t>
+          <t>2,34; 7,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,39</t>
+          <t>2,67; 7,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,0</t>
+          <t>2,91; 6,43</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,81</t>
+          <t>2,1; 4,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,77</t>
+          <t>1,82; 4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,88</t>
+          <t>2,26; 4,02</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2328</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2065</t>
+          <t>631; 4598</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>815; 6031</t>
+          <t>0; 1810</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1155; 6654</t>
+          <t>888; 5263</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5024</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2057</t>
+          <t>1868; 9967</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2452; 10854</t>
+          <t>0; 1664</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2669; 11156</t>
+          <t>1977; 9949</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8540</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1662; 10723</t>
+          <t>941; 8422</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>928; 8311</t>
+          <t>2447; 10728</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4472; 14002</t>
+          <t>4248; 14798</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>23728</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6179; 18218</t>
+          <t>6837; 20847</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6664; 22526</t>
+          <t>6805; 18560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16213; 34777</t>
+          <t>15951; 35203</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11175; 24904</t>
+          <t>14389; 31658</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16282; 35530</t>
+          <t>11233; 25225</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30492; 54260</t>
+          <t>29442; 52502</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/KIDMED_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen una baja adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,69; 12,28</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,24</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 6,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 6,35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,65; 3,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,47; 4,21</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 6,14</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,13; 3,95</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,34; 7,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,67; 7,27</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,91; 6,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 4,61</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,82; 4,08</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2,26; 4,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.05318100540881246</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.007906889091542574</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.02906178038037995</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2328</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.0168686469388343</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01108727270166629</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>631; 4598</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1810</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>888; 5263</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.122826877284262</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.0424161410074348</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.06569109446348993</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.02992455386254309</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.002227328930140277</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.0166034294741622</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4699</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5024</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01189206358498376</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.006533722931201287</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1868; 9967</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 1664</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1977; 9949</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.06346690135919374</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.01143442254106659</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.03288114991814033</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.01742605310910414</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.02892847259803819</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.02278668267900264</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5053</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8540</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.00470381486705648</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01400833612489848</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01133543509355034</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>941; 8422</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2447; 10728</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4248; 14798</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.04208464918334226</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.06141720091584621</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.03948128728082818</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.04172629252362269</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.04517293321064434</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.04333352945491402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>12193</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11534</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>23728</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.02339772715085311</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.02665110424945936</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.0291309865580767</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6837; 20847</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>6805; 18560</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15951; 35203</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.07133921003814785</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.07268723787800042</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.06429061021729057</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.03257159219190062</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.02790148722013043</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.03035931220745052</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>22371</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>17249</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39620</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.02095011880756617</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.0181705949898663</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.02256034144847768</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>14389; 31658</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>11233; 25225</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>29442; 52502</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.04609328257751053</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.04080404033416259</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.04023056483244414</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen una baja adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>631</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4598</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1810</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>5263</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4699</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>324</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>5024</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1868</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9967</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1664</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>9949</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3487</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5053</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>8540</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>941</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2447</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>8422</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10728</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>14798</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>12193</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>11534</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>23728</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6837</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>6805</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>15951</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>20847</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>18560</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>35203</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>22371</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>17249</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>39620</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>14389</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>11233</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>29442</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>31658</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>25225</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>52502</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>